--- a/统计结果_完整版.xlsx
+++ b/统计结果_完整版.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:BG15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -424,183 +424,511 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>类型</t>
+          <t>亚文化</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>母维度</t>
+          <t>产品内涵</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>子维度</t>
+          <t>产品寓意</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>关键词</t>
+          <t>消费心理</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>出现次数</t>
+          <t>意义创新</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>对应语句</t>
+          <t>设计学院</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>设计顾问</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>符号审美</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>艺术合作</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>文化IP联名</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>价值思潮</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>生活方式</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>设计网络</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>情感文化</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>社会文化模式</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>社会文化范式</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>生活形态</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>价值主张</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>产品语言</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>设计平台</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>艺术家</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>外部设计师</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>外包设计</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>产学研合作</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>跨界艺术</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>符号价值</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>身份象征</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>色彩</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>设计总监</t>
+        </is>
+      </c>
+      <c r="AE1" t="inlineStr">
+        <is>
+          <t>生活美学</t>
+        </is>
+      </c>
+      <c r="AF1" t="inlineStr">
+        <is>
+          <t>文化学者</t>
+        </is>
+      </c>
+      <c r="AG1" t="inlineStr">
+        <is>
+          <t>创意顾问</t>
+        </is>
+      </c>
+      <c r="AH1" t="inlineStr">
+        <is>
+          <t>社会文化知识</t>
+        </is>
+      </c>
+      <c r="AI1" t="inlineStr">
+        <is>
+          <t>审美体验</t>
+        </is>
+      </c>
+      <c r="AJ1" t="inlineStr">
+        <is>
+          <t>流行符号</t>
+        </is>
+      </c>
+      <c r="AK1" t="inlineStr">
+        <is>
+          <t>设计展览</t>
+        </is>
+      </c>
+      <c r="AL1" t="inlineStr">
+        <is>
+          <t>产品语义</t>
+        </is>
+      </c>
+      <c r="AM1" t="inlineStr">
+        <is>
+          <t>情感愉悦</t>
+        </is>
+      </c>
+      <c r="AN1" t="inlineStr">
+        <is>
+          <t>造型</t>
+        </is>
+      </c>
+      <c r="AO1" t="inlineStr">
+        <is>
+          <t>跨界合作</t>
+        </is>
+      </c>
+      <c r="AP1" t="inlineStr">
+        <is>
+          <t>首席设计官</t>
+        </is>
+      </c>
+      <c r="AQ1" t="inlineStr">
+        <is>
+          <t>文化机构合作</t>
+        </is>
+      </c>
+      <c r="AR1" t="inlineStr">
+        <is>
+          <t>设计语言</t>
+        </is>
+      </c>
+      <c r="AS1" t="inlineStr">
+        <is>
+          <t>先锋艺术思潮</t>
+        </is>
+      </c>
+      <c r="AT1" t="inlineStr">
+        <is>
+          <t>消费者洞察</t>
+        </is>
+      </c>
+      <c r="AU1" t="inlineStr">
+        <is>
+          <t>设计创新生态</t>
+        </is>
+      </c>
+      <c r="AV1" t="inlineStr">
+        <is>
+          <t>设计守门人</t>
+        </is>
+      </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>用户洞察</t>
+        </is>
+      </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>风格调性</t>
+        </is>
+      </c>
+      <c r="AY1" t="inlineStr">
+        <is>
+          <t>特聘设计师</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>高校合作</t>
+        </is>
+      </c>
+      <c r="BA1" t="inlineStr">
+        <is>
+          <t>设计事务所</t>
+        </is>
+      </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>流行文化</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>美学设计</t>
+        </is>
+      </c>
+      <c r="BD1" t="inlineStr">
+        <is>
+          <t>产品意义</t>
+        </is>
+      </c>
+      <c r="BE1" t="inlineStr">
+        <is>
+          <t>情感价值</t>
+        </is>
+      </c>
+      <c r="BF1" t="inlineStr">
+        <is>
+          <t>科研机构</t>
+        </is>
+      </c>
+      <c r="BG1" t="inlineStr">
+        <is>
+          <t>形式美</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>中国制造2025.txt</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>政策文件</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>产学研设计协同</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>科研机构</t>
-        </is>
-      </c>
-      <c r="F2" t="n">
-        <v>1</v>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>引导外资投向新一代信息技术、高端装备、新材料、生物医药等高端制造领域，鼓励境外企业和科研机构在我国设立全球研发机构。</t>
+          <t>设计驱动型创新理论最新进展评述_陈雪颂.pdf</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>(5)从本文可知，意义创新可以
+创新的主体框架已初步建立，但仍存在一些不足，主要包括：（1）市场和意义创新的概念区
+（3）技术和意义创新两者互动
+其次是技术创新与意义创新的协同问题，主要关系到技术密集型
+需要具备社会文化和技术的双重学习能力，而学习过程就是意义创新中的核心过程。</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>(1)中的关键社会文化知识，第二步是对相关知识进行批判性吸收。</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>(1)提出，但近年来Dell’era和Verganti（2011）才对产品意义扩散中的关键因素和动力机制进</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>制造业设计能力提升专项行动计划.txt</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>政策文件</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>产学研设计协同</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>科研机构</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>鼓励社会团体、高等院校、科研机构和制造业企业协作办学，探索开放式、网络化的设计教学模式，引导更多社会资源投向设计教育领域。</t>
+          <t>设计驱动型创新国内外研究述评与未来展望_徐蕾.pdf</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>制造业设计能力提升专项行动计划.txt</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>政策文件</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>商业设计服务与产业协作生态</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>设计平台</t>
-        </is>
-      </c>
-      <c r="F4" t="n">
-        <v>1</v>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>聚焦装备制造业开放设计平台建设，特种用途或特殊环境装备设计，高端装备关键零部件设计等重点，拟订并发布制造业短板领域设计问题清单，探索利用“揭榜挂帅”机制，引导相关地区和机构联合攻关，加快突破关键核心技术，促进设计成果创新示范应用。</t>
+          <t>设计驱动式创新机理研究_陈雪颂.pdf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>国务院关于推进文化创意和设计服务与相关产业融合发展的若干意见.txt</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>政策文件</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>产学研设计协同</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>科研机构</t>
-        </is>
-      </c>
-      <c r="F5" t="n">
-        <v>2</v>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>积极推进产学研用合作培养人才，发展专业学位研究生教育，扶持和鼓励相关行业和产业园区、龙头企业与普通本科高校、职业院校及科研机构共同建立人才培养基地，支持符合条件的设立博士后科研工作站，探索学历教育与职业培训并举、创意和设计与经营管理结合的人才培养新模式，加快培养高层次、复合型人才。
-鼓励企业、院校、科研机构成立战略联盟，引导创意和设计、科技创新要素向企业聚集，加大联盟知识产权管理能力建设，推行知识产权集群式管理。</t>
+          <t>设计驱动创新微观机理与顾客感知情感价值研究_赖红波.pdf</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>国家级工业设计中心认定管理办法.pdf</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>政策文件</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>美学风格与设计语言</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>造型</t>
-        </is>
-      </c>
-      <c r="F6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>经登记的版权（含产品设计图纸及其说明、设计造型图像等）。</t>
+          <t>设计驱动型创新理论述评与演化趋势：基于有意义的创新框架_陶金元.pdf</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>(5)（Verganti, 2009） 、意义创新 （Verganti, 2016）等新范
+陈雪颂 ,王志玮 ,陈劲 .2016 .外部知识网络嵌入性对企业设计创新绩效的影响机制 :以意义创新
+关注人文精神与哲学思考维度的有意义创新提供
+意义创新为核心 ，秉承以人为中心的设计作为底
+意义和价值意义在内的内部意义创新 ，以及包含</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>(5)有社会文化范式实现突破 ，其中渐进式创新意味
+循当前社会文化范式 ，也即主流社会文化符号的
+ganti, 2003），强调通过突破社会文化范式 （socio -
+（既有社会文化范式 ）设计驱动型创新··10第07期 设计驱动型创新理论述评与演化趋势 ：基于有意义
+设计驱动型创新从社会文化范式演进出发 ，超</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>(1)柳卸林 ,王倩 .2021 .面向核心价值主张的创新生态系统演化 [J].科学学研究 ,39(6):</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>(5)产品内在意义 （产品语言 ）为核心目标 ，要求重新
+新的内在意义 ，进而形成新的 “产品语言 ” ，实现颠
+内在意义 ，借助创新网络实现新的产品语言形式
+工艺） 、内在意义 （产品语言 ） ，把市场需求排除在
+化成产品意义以新的特定产品语言传递给消费</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>(2)注：I1、I2…… In代表艺术家 、文化机构 、媒体、设计师、供应商、销售商等各类诠释者··13第
+的诠释者创新网络 ，包括了艺术家 、文化机构 、社</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>(1)型、尺寸、样式、色彩等）方面的优化 ；</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>(5)诠释者网络基于社会文化知识进行创新 ，通过设
+糊了组织的边界并内化外部社会文化知识和各种
+广泛倾听为开端 ，就社会文化知识 （范式和趋势 ）
+资源、社会文化知识 、有关产品创新的知识 、技术
+全新理念和愿景 诠释 倾听 社会文化知识</t>
+        </is>
+      </c>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>(5)后，设计驱动型创新强调产品意义源于社会文化
+化成产品意义以新的特定产品语言传递给消费
+2012） ，推动文化与技术的整合并实现产品意义共
+在于技术 、市场、产品意义所构成的三维边界内 。
+出的“意义创新 ”也停留在产品意义探索和应用开</t>
+        </is>
+      </c>
+      <c r="BE6" t="inlineStr">
+        <is>
+          <t>(1)赖红波 .2019 .设计驱动创新微观机理与顾客感知情感价值研究 [J].科研管理 ,40(3):1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>设计驱动在企业创新行为中的地位研究_陈国栋.pdf</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>(1)确立了以设计为核心的战略发展方向，不断与高校设计学院、国外设计机构合作，企业内部专职设计人员</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>(1)用于创新，筹建了具有国内先进水平的炊具外观造型工业设计、模</t>
+        </is>
+      </c>
+      <c r="BA7" t="inlineStr">
+        <is>
+          <t>(1)部设计团队、整合国内优秀设计团队、与国际设计事务所合作等形式的产品设计开发模式。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>网络异质性如何提升创新绩效_——基于设计驱动型创新解析视角的实证研究_徐蕾 (1).pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>设计驱动型创新机理的实证研究_叶伟巍.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>（提高了制造业升级）设计驱动型创新系统构建与产业转型升级机制研究-赖红波.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>企业设计创新能力的构成及培养研究——产品语义学视角_俞湘珍.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>协同创新网络视角下设计驱动式创新实现路径研究_卢启程.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>中国制造2025.txt</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>(1)引导外资投向新一代信息技术、高端装备、新材料、生物医药等高端制造领域，鼓励境外企业和科研机构在我国设</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>制造业设计能力提升专项行动计划.txt</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>(1)聚焦装备制造业开放设计平台建设，特种用途或特殊环境装备设计，高端装备关键零部件设计等重点，拟订并发布</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>(1)鼓励社会团体、高等院校、科研机构和制造业企业协作办学，探索开放式、网络化的设计教学模式，引导更多社会</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>国务院关于推进文化创意和设计服务与相关产业融合发展的若干意见.txt</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>(2)鼓励企业、院校、科研机构成立战略联盟，引导创意和设计、科技创新要素向企业聚集，加大联盟知识产权管理能
+积极推进产学研用合作培养人才，发展专业学位研究生教育，扶持和鼓励相关行业和产业园区、龙头企业与普通本</t>
         </is>
       </c>
     </row>
